--- a/光伏配储项目/电价数据/2026/弼臣站.xlsx
+++ b/光伏配储项目/电价数据/2026/弼臣站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.31592</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.31363</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27665</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29096</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.26863</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.27566</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.26509</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.28294</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.27065</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.25178</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.17056</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.17038</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.19214</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.28212</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07310999999999999</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.23103</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.02207</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17082</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.2648</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25211</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.25673</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24139</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.27912</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.18015</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29892</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.4093</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.39237</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.03468</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.49628</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.39209</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.54976</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.20028</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.1033</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.85041</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.03043</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.01852</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.79595</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.14316</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.45085</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.47161</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.47755</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.14197</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.47309</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.48293</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.39791</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.32474</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.50549</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.31762</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.30824</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.29027</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.27154</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.32248</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.12607</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.21129</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.6529700000000001</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.61363</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.29327</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.42952</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.18774</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.29258</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.20629</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.10624</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.07665000000000001</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.3098399999999999</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.7882899999999999</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.8016</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.8047799999999999</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.79374</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.80161</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.8422000000000001</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.86633</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.02876</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.82662</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.5997100000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.80255</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.38401</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.8278099999999999</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7880499999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.8196599999999999</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.49813</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.83688</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.50831</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.40652</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.32282</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.32569</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.2686</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.27412</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.32361</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.30416</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.30805</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.30737</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.36671</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.11078</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.16123</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.23109</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.30059</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.31244</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.05492</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.29961</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.29907</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.27543</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.28554</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.73595</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.76213</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.7911699999999999</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.28308</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.2755</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.18154</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.20526</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.25617</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.44822</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.07773999999999999</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45832</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51212</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5136000000000001</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.51219</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.55162</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.53307</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.62859</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.4076</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.70621</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.42471</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50245</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.51223</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.4643</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.64791</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.45956</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.40093</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.37369</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.4754</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.43464</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.4935</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.49145</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.44416</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.4634</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.50743</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.33607</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.33081</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32248</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44469</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.48392</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.46732</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37811</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.07659999999999999</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.29506</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.79064</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.09731999999999999</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.10092</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.13387</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.29046</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>-0.007820000000000001</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.20907</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.15571</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>-0.02215</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.10561</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45064</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.66859</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.35773</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50244</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.30186</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30322</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.30882</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30491</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.29934</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.26106</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>-0.01755</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36307</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31334</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30046</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.2895</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14358</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02606</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.30317</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.29825</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.30272</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40601</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26455</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.2567</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.23919</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.10396</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.26725</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.02891</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26349</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30486</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34733</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.41298</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42536</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31844</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.09884999999999999</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.24831</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.25359</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.05468</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.08615</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.29039</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.19661</v>
+      </c>
+      <c r="L122" t="n">
+        <v>-0.02188</v>
+      </c>
+      <c r="M122" t="n">
+        <v>-0.03244</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.25265</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.08018</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.2512</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.21925</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.19741</v>
+      </c>
+      <c r="W122" t="n">
+        <v>-0.02169</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.17952</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30644</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.25241</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.27346</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.20635</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.2689</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>-0.04979</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>-0.04972</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01012</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.2064</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04936</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27571</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19404</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.01154</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06055</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05876</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31648</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30311</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.6944600000000001</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.29902</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.05529</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.77083</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87038</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.65822</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5738300000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.41651</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.40652</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39304</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37812</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38848</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39952</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44393</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36496</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.39277</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.44802</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.49579</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.44502</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.27081</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.60914</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.32383</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.29183</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.30508</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29239</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26719</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.19626</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.29639</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.29141</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.30551</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28623</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29364</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30792</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29545</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.18444</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26417</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26401</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.2785</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26377</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.28265</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29363</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.30161</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29545</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.30634</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.3067</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30761</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.29333</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32464</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.78704</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.29928</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.29951</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.29707</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.30215</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.29872</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29517</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.29451</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29722</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.20746</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.20308</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.29484</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29569</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29742</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.27924</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.07582999999999999</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>-0.02253</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29276</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29739</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.07429999999999999</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30389</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>-0.02159</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>-0.0177</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.08512</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.0205</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.27611</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.37884</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.03524</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.45055</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.11144</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>-0.02064</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.02554</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.00766</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>-0.02485</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>-0.0195</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>-0.01708</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>-0.03779</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>-0.02969</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>-0.03061</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>-0.02697</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>-0.03134</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.07058</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>-0.01843</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>-0.0233</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>-0.01897</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>-0.02037</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>-0.01879</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>-0.00911</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>-0.02483</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>-0.01939</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>-0.01928</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>-0.01625</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>-0.02098</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>-0.01879</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>-0.0186</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>-0.01745</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>-0.01688</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>-0.02041</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.07568000000000001</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>-0.01989</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>-0.00872</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>-0.01701</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>-0.01288</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>-0.01987</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>-0.01803</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.21641</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>-0.01967</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>-0.01999</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>-0.01873</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>-0.03159</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.00797</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F126" t="n">
+        <v>-0.01214</v>
+      </c>
+      <c r="G126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H126" t="n">
+        <v>-0.01875</v>
+      </c>
+      <c r="I126" t="n">
+        <v>-0.0295</v>
+      </c>
+      <c r="J126" t="n">
+        <v>-0.03119</v>
+      </c>
+      <c r="K126" t="n">
+        <v>-0.02006</v>
+      </c>
+      <c r="L126" t="n">
+        <v>-0.01655</v>
+      </c>
+      <c r="M126" t="n">
+        <v>-0.01226</v>
+      </c>
+      <c r="N126" t="n">
+        <v>-0.01805</v>
+      </c>
+      <c r="O126" t="n">
+        <v>-0.01978</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.08990000000000001</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>-0.01649</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.08456</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.04846</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.10535</v>
+      </c>
+      <c r="U126" t="n">
+        <v>-0.01538</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.25482</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>-0.04329</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.04173</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.20885</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.26005</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.15319</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>-0.04925</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.23546</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.07271999999999999</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.15404</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.24241</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.25417</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33435</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.01268</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.03777</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>-0.02129</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.28474</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.24414</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.28729</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.24959</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.20917</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.22517</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.05596</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.1418</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.05038</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.18864</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>-0.00126</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30071</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.05335</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.04425</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.08047</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.11491</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>-0.02256</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.05131</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.2017</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.0544</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.24312</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.25166</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>-0.01875</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.25759</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.04499</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.06569</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.08663999999999999</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.0843</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.08605</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.07948999999999999</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.06643</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.10566</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.08428000000000001</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.07045</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.11189</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.08354</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.08554</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.20186</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>-0.01757</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.08439000000000001</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.28781</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.09486</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.07845999999999999</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.29514</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.23642</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.06461</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.22649</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>-0.02391</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.06692000000000001</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.05944</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.02965</v>
+      </c>
+      <c r="F127" t="n">
+        <v>-0.03161</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.04952</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.19278</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.03455</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.18994</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.02523</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.05144</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.05952</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.05779</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.07068000000000001</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.06931999999999999</v>
+      </c>
+      <c r="R127" t="n">
+        <v>-0.04968</v>
+      </c>
+      <c r="S127" t="n">
+        <v>-0.03669</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.04040999999999999</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.04439</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.03992</v>
+      </c>
+      <c r="X127" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.19544</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.04037</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.0218</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.02088</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.03613</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.06404</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.17054</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.03129</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.14085</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.02675</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.2488</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>-0.01004</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.12351</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.04563</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.04833</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.28813</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.11705</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.24032</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.0562</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.12464</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.05061</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.04948</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.16667</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28227</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.24682</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.21397</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.26631</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.24718</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.2644</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.20856</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.24262</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.26649</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.25539</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.23543</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.27558</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.26213</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.27426</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.29773</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30404</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.28406</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.28633</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.30076</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30151</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.27561</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.2736</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.2747</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.28523</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.27421</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.28829</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.27472</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.28646</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.39468</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.26971</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.26793</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28726</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28954</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.25308</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.28395</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.2914</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.30153</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30592</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29763</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.30166</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29726</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29766</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.30667</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29863</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30266</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.29289</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29597</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.28857</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28285</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.28635</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30353</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28539</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28362</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.23522</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30229</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28826</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.29641</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.29107</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27956</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30832</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29506</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24574</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28796</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.29149</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.36853</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.43171</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.30102</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30464</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30544</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.29148</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28957</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29445</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29611</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.2997</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.30169</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29741</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.2954</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30666</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29816</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29759</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30653</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.39619</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.99426</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41183</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.62802</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38782</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.4767</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.49373</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.38029</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.43038</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.48523</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38581</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.42427</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.39525</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.53754</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27825</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.26721</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.18946</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.42834</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.18807</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.19842</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.43681</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.41549</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.40097</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.5275700000000001</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.42306</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.42816</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.11854</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.10586</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>-0.00238</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.01335</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.43881</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.4247</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>-0.00117</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.14806</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.62537</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38395</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.26068</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.09240999999999999</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.46933</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>-0.02382</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.10004</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.0501</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.07084</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.24203</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>-0.02665</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28774</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.04812</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>-0.02666</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.28266</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.18082</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38588</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.27299</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27633</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.27993</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.28025</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.20523</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.19719</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.26994</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.28004</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.2769</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.26888</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.26877</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27638</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.19906</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29665</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.19637</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.1615</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23906</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.20008</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.00018</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.1961</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.20176</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.01703</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.20891</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.17502</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.16612</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.16913</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.20536</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.23969</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.2997</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.30305</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.21145</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.26527</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.24649</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.30174</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.29935</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.24245</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>-0.0158</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.24427</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.22603</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.25872</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.22797</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.23203</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.20771</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29763</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.19561</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.2386</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.22176</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.23844</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.2015</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.19547</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.06758</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.18748</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.19993</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.23046</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.25604</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.1563</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.24989</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.27792</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.22871</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.26261</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.30227</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.27362</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.30197</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.27462</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28946</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.28926</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.2776</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.27784</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.2894</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.21702</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.29349</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.20977</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.28385</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.27922</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.31582</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>-0.00095</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.23954</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.3186</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29458</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.2838</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.00034</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.29169</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28833</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27649</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28799</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.28698</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28544</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.28654</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28759</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27599</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28646</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.29238</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.29191</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.28306</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27652</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.2869</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27658</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28696</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.27214</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29291</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.3008</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30184</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30734</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30569</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.39402</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34719</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.56672</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.53322</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.21321</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.31101</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29884</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38254</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28789</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.41328</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.41311</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.3722</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.39048</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.37297</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.45012</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.50449</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.59548</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.56086</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.60749</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.7427999999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.42666</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.38813</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.46967</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.4289</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3163</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36612</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.31537</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.31294</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.31472</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.29242</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.29959</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.28966</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.30398</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.45186</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.42768</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.36748</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.3732200000000001</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40596</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.36355</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>-0.00623</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.2544</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.27427</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.03091</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.28618</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.22183</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.28396</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.30584</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.2133</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.27553</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.30305</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.29767</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.30732</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.30597</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.30611</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.5385</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64388</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.32293</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40588</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39582</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38755</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.27476</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.29187</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.29617</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.01446</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.27995</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28723</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.28073</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.28774</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.29479</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.28579</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.18465</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.28608</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.00012</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.28538</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.30029</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.29551</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.20026</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.04141</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.24949</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.006480000000000001</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04824000000000001</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>-0.04007</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.20963</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.20775</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>-0.04036</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-0.02127</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.01963</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.00495</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>-0.03555</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>-0.04306</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>-0.02542</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.20009</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.19766</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.19939</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.19882</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>-0.03997999999999999</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.30059</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.27641</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.21909</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.23961</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>-0.03457</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.14356</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.3889</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.29694</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37951</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>-0.00677</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>-0.01369</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>-0.01728</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>-0.01646</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.07393000000000001</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.05434000000000001</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>-0.00646</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.28334</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.1723</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.00567</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>-0.04991</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.006730000000000001</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>-0.03563</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>-0.04355</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>-0.02277</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>-0.0235</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>-0.02272</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.11609</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.28395</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.18112</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.11578</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.18648</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.2774</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.20079</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.1749</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.01329</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.24415</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.00959</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.00991</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.17511</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.0009</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.20645</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.27936</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.17393</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.00859</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.16415</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.00044</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.1664</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.16921</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.17202</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.00759</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.17483</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.00742</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.0166</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.1861</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.18781</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.15636</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.24012</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.03846</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.2512</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.05758</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.19761</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.10478</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.14251</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.26138</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.02074</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.28284</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.30338</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.24839</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.19681</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.16744</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.00222</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.01735</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.00929</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>-0.00023</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.22321</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.20784</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.14182</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.02358</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.01295</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.00319</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>-0.00513</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.004200000000000001</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.01005</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>-0.00492</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.009730000000000001</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.01575</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.15829</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.15502</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.00903</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.00017</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.20631</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.15949</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.17465</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.03711</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.12562</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.16176</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.01731</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>-0.0343</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.03696</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.01713</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>-0.02941</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.22585</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.06503</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.02086</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.25156</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.02499</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.20673</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.22913</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.22566</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.09706999999999999</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.10866</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.22934</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.07751000000000001</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.20506</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.02693</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.01895</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.1983</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.21375</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.23474</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.25252</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.28032</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27582</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.05361</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.19047</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.18743</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26862</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.00102</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.20632</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.22654</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.21843</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.04226</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.01201</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.00123</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.00121</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.00065</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.00065</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.00099</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.20101</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.01251</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.00065</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.18114</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.00224</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.00308</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24566</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.03705</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.00624</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00035</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02203</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.04072</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04297</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04089</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02936</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.04956</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.22521</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.10031</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.20555</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.20715</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.21219</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.20759</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.20951</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.00193</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.1884</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.24497</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28262</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29593</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30108</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.25814</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29639</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.28508</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29317</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.24708</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.21946</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.27776</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.30125</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.29193</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.29627</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30107</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.24032</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.30031</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29972</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.27251</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.03382</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28446</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.29214</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.28324</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.17746</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.17197</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.17644</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.17373</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.01995</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.16971</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.15824</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.01903</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.04972</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.04834</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.02149</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.01868</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.00907</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.01523</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.20089</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.20044</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>-0.04936</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.04848</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.04892000000000001</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.04606</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85068</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86177</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09278</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.00027</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.25101</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28038</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29668</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.04781000000000001</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.46698</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29239</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.0688</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30253</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30716</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.66451</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.50752</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.38086</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.43528</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.74573</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.83558</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.39407</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.57028</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.43875</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.62612</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.71347</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.7117</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.7149</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.79183</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.43264</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.31063</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.33734</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.4409</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.31472</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.27684</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.26997</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.19964</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.26287</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.25824</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.25137</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.22061</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.26916</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.20835</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.17488</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.20384</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.1692</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.17196</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.0205</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.16758</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.19016</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.23893</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.29183</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.24758</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.25727</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29903</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.25639</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.27858</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.31167</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.38221</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.2585</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30212</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31363</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33653</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39861</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.29874</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.29452</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29644</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.30011</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.30227</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.30234</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.15896</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29656</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.41201</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.44639</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.26621</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.72151</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.75536</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40977</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.44027</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5062099999999999</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.65422</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.75773</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.41709</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.35609</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42835</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.20309</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31891</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.38534</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30751</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30665</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.30195</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29601</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30721</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.30631</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31737</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33264</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39098</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43461</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36676</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33597</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.34298</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37152</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.36489</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.38612</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.37297</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.57743</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.7250599999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.6401399999999999</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.55188</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.39655</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3235</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28674</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29842</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.29232</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31424</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.02084</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29155</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.28639</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29412</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.28539</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30711</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.38146</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.27249</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.43359</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.39537</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.20029</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29965</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.4355</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.54414</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.3439700000000001</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.15273</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.19425</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.46848</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.33378</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.31116</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32769</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.65844</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.41571</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.40882</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.36259</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35281</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.1885</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.30239</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.27734</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30548</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.03956</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.03537</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.20137</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>-0.01755</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.28022</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.21878</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.12637</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33956</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="E143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F143" t="n">
+        <v>-0.04983</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.23017</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17608</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29569</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14574</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19862</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14609</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28757</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04759</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12158</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22599</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26022</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14397</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14527</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28367</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18819</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.26887</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22681</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.03456</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-0.04007</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.22823</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.09545000000000001</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.20524</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.02883</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.04712</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.21457</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.13467</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.23714</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.27831</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.22327</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.16645</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.13669</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.07202</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.26772</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.42149</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.39794</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.22538</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.03893</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>-0.02103</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>-0.01986</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.02885</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.27575</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.05681</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.04036</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38613</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.3445299999999999</v>
       </c>
     </row>
   </sheetData>
